--- a/data/informe_servidores_20260526.xlsx
+++ b/data/informe_servidores_20260526.xlsx
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generado el: 26/05/2026 09:51</t>
+          <t>Generado el: 26/05/2026 10:16</t>
         </is>
       </c>
     </row>

--- a/data/informe_servidores_20260526.xlsx
+++ b/data/informe_servidores_20260526.xlsx
@@ -500,7 +500,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generado el: 26/05/2026 10:16</t>
+          <t>Generado el: 26/05/2026 10:33</t>
         </is>
       </c>
     </row>
